--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,4013 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127421259</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>593896</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6980329</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127420137</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593873</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6980393</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127421406</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>593921</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6980392</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127419655</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593933</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6980566</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127419866</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>593940</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6980501</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127419826</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>593938</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6980539</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127419978</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>593931</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6980442</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127420036</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>593889</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6980419</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127419287</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>593904</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6980639</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127421018</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>593762</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6980239</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127420104</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>593888</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6980408</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127420313</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartviken, Svartviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>593881</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6980236</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127419756</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sundet, Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>593943</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6980552</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127421272</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>593916</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6980341</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127421852</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sundet, Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>593957</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6980531</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127419767</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundet, Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>593943</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6980554</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127420409</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svartviken, Svartviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>593897</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6980226</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127420121</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>593878</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6980391</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127420237</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>593891</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6980346</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127421539</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>353</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>593955</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6980435</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127420002</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>593907</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6980443</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127419220</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>353</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>593901</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6980651</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127420170</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>593884</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6980384</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127419859</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92809</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>593940</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6980502</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127419760</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>353</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sundet, Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>593943</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6980554</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127421307</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>593909</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6980352</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127419008</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>593907</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6980678</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127419922</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>593925</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6980436</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127421509</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>593953</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6980432</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127421293</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>353</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>593913</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6980334</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127420200</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>593873</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6980365</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127420388</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svartviken, Svartviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>593888</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6980235</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127420401</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svartviken, Svartviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>593888</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6980242</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127420375</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>353</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svartviken, Svartviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>593879</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6980223</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127419973</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>593919</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6980452</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127420990</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>593785</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6980249</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127421707</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>593964</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6980471</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127419778</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sundet, Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>593943</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6980554</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127419423</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sundet, Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>593923</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6980636</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127421244</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>593884</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6980318</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127421181</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>593779</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6980274</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127419655</v>
+        <v>127419866</v>
       </c>
       <c r="B10" t="n">
         <v>92616</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593933</v>
+        <v>593940</v>
       </c>
       <c r="R10" t="n">
-        <v>6980566</v>
+        <v>6980501</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127419866</v>
+        <v>127419655</v>
       </c>
       <c r="B11" t="n">
         <v>92616</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593940</v>
+        <v>593933</v>
       </c>
       <c r="R11" t="n">
-        <v>6980501</v>
+        <v>6980566</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,32 +1720,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419826</v>
+        <v>127419978</v>
       </c>
       <c r="B12" t="n">
-        <v>92616</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593938</v>
+        <v>593931</v>
       </c>
       <c r="R12" t="n">
-        <v>6980539</v>
+        <v>6980442</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,45 +1817,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419978</v>
+        <v>127420313</v>
       </c>
       <c r="B13" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593931</v>
+        <v>593881</v>
       </c>
       <c r="R13" t="n">
-        <v>6980442</v>
+        <v>6980236</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2011,45 +2011,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419287</v>
+        <v>127419826</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593904</v>
+        <v>593938</v>
       </c>
       <c r="R15" t="n">
-        <v>6980639</v>
+        <v>6980539</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127421018</v>
+        <v>127419287</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,39 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593762</v>
+        <v>593904</v>
       </c>
       <c r="R16" t="n">
-        <v>6980239</v>
+        <v>6980639</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2184,11 +2179,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,45 +2302,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127420313</v>
+        <v>127421018</v>
       </c>
       <c r="B18" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593881</v>
+        <v>593762</v>
       </c>
       <c r="R18" t="n">
-        <v>6980236</v>
+        <v>6980239</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2383,6 +2378,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B20" t="n">
-        <v>79632</v>
+        <v>92620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R20" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B21" t="n">
-        <v>92620</v>
+        <v>79632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R21" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2894,50 +2894,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127420121</v>
+        <v>127420002</v>
       </c>
       <c r="B24" t="n">
-        <v>56849</v>
+        <v>78772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593878</v>
+        <v>593907</v>
       </c>
       <c r="R24" t="n">
-        <v>6980391</v>
+        <v>6980443</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2970,11 +2965,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3001,10 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420237</v>
+        <v>127420121</v>
       </c>
       <c r="B25" t="n">
-        <v>92628</v>
+        <v>56849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,34 +3002,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593891</v>
+        <v>593878</v>
       </c>
       <c r="R25" t="n">
-        <v>6980346</v>
+        <v>6980391</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3072,6 +3067,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3098,32 +3098,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421539</v>
+        <v>127420237</v>
       </c>
       <c r="B26" t="n">
-        <v>78681</v>
+        <v>92628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593955</v>
+        <v>593891</v>
       </c>
       <c r="R26" t="n">
-        <v>6980435</v>
+        <v>6980346</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420002</v>
+        <v>127421539</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,21 +3206,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593907</v>
+        <v>593955</v>
       </c>
       <c r="R27" t="n">
-        <v>6980443</v>
+        <v>6980435</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R31" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B32" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R32" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3777,45 +3777,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419008</v>
+        <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593907</v>
+        <v>593925</v>
       </c>
       <c r="R33" t="n">
-        <v>6980678</v>
+        <v>6980436</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3874,45 +3874,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127419922</v>
+        <v>127419008</v>
       </c>
       <c r="B34" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593925</v>
+        <v>593907</v>
       </c>
       <c r="R34" t="n">
-        <v>6980436</v>
+        <v>6980678</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4068,32 +4068,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B36" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R36" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420200</v>
+        <v>127420388</v>
       </c>
       <c r="B37" t="n">
         <v>92616</v>
@@ -4196,14 +4196,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593873</v>
+        <v>593888</v>
       </c>
       <c r="R37" t="n">
-        <v>6980365</v>
+        <v>6980235</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4262,45 +4262,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420388</v>
+        <v>127421293</v>
       </c>
       <c r="B38" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593888</v>
+        <v>593913</v>
       </c>
       <c r="R38" t="n">
-        <v>6980235</v>
+        <v>6980334</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420401</v>
+        <v>127420375</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593888</v>
+        <v>593879</v>
       </c>
       <c r="R39" t="n">
-        <v>6980242</v>
+        <v>6980223</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127420375</v>
+        <v>127420401</v>
       </c>
       <c r="B40" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593879</v>
+        <v>593888</v>
       </c>
       <c r="R40" t="n">
-        <v>6980223</v>
+        <v>6980242</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127419423</v>
+        <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593923</v>
+        <v>593884</v>
       </c>
       <c r="R45" t="n">
-        <v>6980636</v>
+        <v>6980318</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R46" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5145,10 +5145,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421181</v>
+        <v>127419423</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,34 +5156,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593779</v>
+        <v>593923</v>
       </c>
       <c r="R47" t="n">
-        <v>6980274</v>
+        <v>6980636</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419978</v>
+        <v>127420313</v>
       </c>
       <c r="B12" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593931</v>
+        <v>593881</v>
       </c>
       <c r="R12" t="n">
-        <v>6980442</v>
+        <v>6980236</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420313</v>
+        <v>127420036</v>
       </c>
       <c r="B13" t="n">
         <v>92616</v>
@@ -1848,14 +1848,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593881</v>
+        <v>593889</v>
       </c>
       <c r="R13" t="n">
-        <v>6980236</v>
+        <v>6980419</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420036</v>
+        <v>127419826</v>
       </c>
       <c r="B14" t="n">
         <v>92616</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593889</v>
+        <v>593938</v>
       </c>
       <c r="R14" t="n">
-        <v>6980419</v>
+        <v>6980539</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,45 +2011,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419826</v>
+        <v>127419287</v>
       </c>
       <c r="B15" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593938</v>
+        <v>593904</v>
       </c>
       <c r="R15" t="n">
-        <v>6980539</v>
+        <v>6980639</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127419287</v>
+        <v>127420104</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,34 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593904</v>
+        <v>593888</v>
       </c>
       <c r="R16" t="n">
-        <v>6980639</v>
+        <v>6980408</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420104</v>
+        <v>127419978</v>
       </c>
       <c r="B17" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593888</v>
+        <v>593931</v>
       </c>
       <c r="R17" t="n">
-        <v>6980408</v>
+        <v>6980442</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127420002</v>
+        <v>127421539</v>
       </c>
       <c r="B24" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2905,21 +2905,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593907</v>
+        <v>593955</v>
       </c>
       <c r="R24" t="n">
-        <v>6980443</v>
+        <v>6980435</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2991,50 +2991,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420121</v>
+        <v>127419220</v>
       </c>
       <c r="B25" t="n">
-        <v>56849</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593878</v>
+        <v>593901</v>
       </c>
       <c r="R25" t="n">
-        <v>6980391</v>
+        <v>6980651</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3067,11 +3062,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3098,32 +3088,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420237</v>
+        <v>127420002</v>
       </c>
       <c r="B26" t="n">
-        <v>92628</v>
+        <v>78772</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593891</v>
+        <v>593907</v>
       </c>
       <c r="R26" t="n">
-        <v>6980346</v>
+        <v>6980443</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3195,45 +3185,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127421539</v>
+        <v>127420121</v>
       </c>
       <c r="B27" t="n">
-        <v>78681</v>
+        <v>56849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593955</v>
+        <v>593878</v>
       </c>
       <c r="R27" t="n">
-        <v>6980435</v>
+        <v>6980391</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3266,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,45 +3292,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127419220</v>
+        <v>127420237</v>
       </c>
       <c r="B28" t="n">
-        <v>78681</v>
+        <v>92628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593901</v>
+        <v>593891</v>
       </c>
       <c r="R28" t="n">
-        <v>6980651</v>
+        <v>6980346</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -5240,6 +5240,216 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127421618</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91621</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Resinoporia crassa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Audet</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>593960</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6980435</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127421800</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91615</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>71</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sundet, Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>593948</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6980547</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>127421259</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>127420137</v>
       </c>
       <c r="B8" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>127421406</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>127419866</v>
       </c>
       <c r="B10" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>127419655</v>
       </c>
       <c r="B11" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420313</v>
+        <v>127420036</v>
       </c>
       <c r="B12" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,14 +1751,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593881</v>
+        <v>593889</v>
       </c>
       <c r="R12" t="n">
-        <v>6980236</v>
+        <v>6980419</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420036</v>
+        <v>127419826</v>
       </c>
       <c r="B13" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593889</v>
+        <v>593938</v>
       </c>
       <c r="R13" t="n">
-        <v>6980419</v>
+        <v>6980539</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419826</v>
+        <v>127420313</v>
       </c>
       <c r="B14" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,14 +1945,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593938</v>
+        <v>593881</v>
       </c>
       <c r="R14" t="n">
-        <v>6980539</v>
+        <v>6980236</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2014,7 +2014,7 @@
         <v>127419287</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>127420104</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127419978</v>
+        <v>127421018</v>
       </c>
       <c r="B17" t="n">
-        <v>78773</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,34 +2216,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593931</v>
+        <v>593762</v>
       </c>
       <c r="R17" t="n">
-        <v>6980442</v>
+        <v>6980239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2276,6 +2281,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2302,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127421018</v>
+        <v>127419978</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>78777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,39 +2323,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593762</v>
+        <v>593931</v>
       </c>
       <c r="R18" t="n">
-        <v>6980239</v>
+        <v>6980442</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2378,11 +2383,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,7 +2412,7 @@
         <v>127419756</v>
       </c>
       <c r="B19" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127421852</v>
       </c>
       <c r="B20" t="n">
-        <v>92620</v>
+        <v>92624</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>127421272</v>
       </c>
       <c r="B21" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>127420409</v>
       </c>
       <c r="B23" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2894,32 +2894,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127421539</v>
+        <v>127420237</v>
       </c>
       <c r="B24" t="n">
-        <v>78681</v>
+        <v>92632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593955</v>
+        <v>593891</v>
       </c>
       <c r="R24" t="n">
-        <v>6980435</v>
+        <v>6980346</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2991,45 +2991,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127419220</v>
+        <v>127420121</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>56853</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593901</v>
+        <v>593878</v>
       </c>
       <c r="R25" t="n">
-        <v>6980651</v>
+        <v>6980391</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3062,6 +3067,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3088,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420002</v>
+        <v>127421539</v>
       </c>
       <c r="B26" t="n">
-        <v>78772</v>
+        <v>78685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593907</v>
+        <v>593955</v>
       </c>
       <c r="R26" t="n">
-        <v>6980443</v>
+        <v>6980435</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3185,50 +3195,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420121</v>
+        <v>127419220</v>
       </c>
       <c r="B27" t="n">
-        <v>56849</v>
+        <v>78685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593878</v>
+        <v>593901</v>
       </c>
       <c r="R27" t="n">
-        <v>6980391</v>
+        <v>6980651</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3261,11 +3266,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,32 +3292,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420237</v>
+        <v>127420002</v>
       </c>
       <c r="B28" t="n">
-        <v>92628</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593891</v>
+        <v>593907</v>
       </c>
       <c r="R28" t="n">
-        <v>6980346</v>
+        <v>6980443</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B29" t="n">
-        <v>92616</v>
+        <v>92813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R29" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B30" t="n">
-        <v>92809</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R30" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B31" t="n">
-        <v>92616</v>
+        <v>78685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R31" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B32" t="n">
-        <v>78681</v>
+        <v>92620</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R32" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3780,7 +3780,7 @@
         <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>127419008</v>
       </c>
       <c r="B34" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>127421509</v>
       </c>
       <c r="B35" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4068,32 +4068,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420200</v>
+        <v>127421293</v>
       </c>
       <c r="B36" t="n">
-        <v>92616</v>
+        <v>78685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593873</v>
+        <v>593913</v>
       </c>
       <c r="R36" t="n">
-        <v>6980365</v>
+        <v>6980334</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4168,7 +4168,7 @@
         <v>127420388</v>
       </c>
       <c r="B37" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B38" t="n">
-        <v>78681</v>
+        <v>92620</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R38" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4362,7 +4362,7 @@
         <v>127420375</v>
       </c>
       <c r="B39" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>127420401</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>127419973</v>
       </c>
       <c r="B41" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>127420990</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421707</v>
+        <v>127419778</v>
       </c>
       <c r="B43" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,34 +4768,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593964</v>
+        <v>593943</v>
       </c>
       <c r="R43" t="n">
-        <v>6980471</v>
+        <v>6980554</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127419778</v>
+        <v>127421707</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,34 +4865,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593943</v>
+        <v>593964</v>
       </c>
       <c r="R44" t="n">
-        <v>6980554</v>
+        <v>6980471</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4954,7 +4954,7 @@
         <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>127419423</v>
       </c>
       <c r="B47" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420036</v>
+        <v>127419287</v>
       </c>
       <c r="B12" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593889</v>
+        <v>593904</v>
       </c>
       <c r="R12" t="n">
-        <v>6980419</v>
+        <v>6980639</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419826</v>
+        <v>127420104</v>
       </c>
       <c r="B13" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593938</v>
+        <v>593888</v>
       </c>
       <c r="R13" t="n">
-        <v>6980539</v>
+        <v>6980408</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,45 +1914,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420313</v>
+        <v>127421018</v>
       </c>
       <c r="B14" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593881</v>
+        <v>593762</v>
       </c>
       <c r="R14" t="n">
-        <v>6980236</v>
+        <v>6980239</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1985,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419287</v>
+        <v>127419978</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,34 +2032,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593904</v>
+        <v>593931</v>
       </c>
       <c r="R15" t="n">
-        <v>6980639</v>
+        <v>6980442</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,45 +2118,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420104</v>
+        <v>127420313</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593888</v>
+        <v>593881</v>
       </c>
       <c r="R16" t="n">
-        <v>6980408</v>
+        <v>6980236</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,50 +2215,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127421018</v>
+        <v>127420036</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593762</v>
+        <v>593889</v>
       </c>
       <c r="R17" t="n">
-        <v>6980239</v>
+        <v>6980419</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2281,11 +2286,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,32 +2312,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127419978</v>
+        <v>127419826</v>
       </c>
       <c r="B18" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593931</v>
+        <v>593938</v>
       </c>
       <c r="R18" t="n">
-        <v>6980442</v>
+        <v>6980539</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B20" t="n">
-        <v>92624</v>
+        <v>79636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R20" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>92624</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2991,50 +2991,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420121</v>
+        <v>127421539</v>
       </c>
       <c r="B25" t="n">
-        <v>56853</v>
+        <v>78685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593878</v>
+        <v>593955</v>
       </c>
       <c r="R25" t="n">
-        <v>6980391</v>
+        <v>6980435</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3067,11 +3062,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3098,7 +3088,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421539</v>
+        <v>127419220</v>
       </c>
       <c r="B26" t="n">
         <v>78685</v>
@@ -3129,14 +3119,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593955</v>
+        <v>593901</v>
       </c>
       <c r="R26" t="n">
-        <v>6980435</v>
+        <v>6980651</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3195,45 +3185,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127419220</v>
+        <v>127420121</v>
       </c>
       <c r="B27" t="n">
-        <v>78685</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593901</v>
+        <v>593878</v>
       </c>
       <c r="R27" t="n">
-        <v>6980651</v>
+        <v>6980391</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3266,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B29" t="n">
-        <v>92813</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R29" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>92813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R30" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R31" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B32" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R32" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3777,45 +3777,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419922</v>
+        <v>127419008</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593925</v>
+        <v>593907</v>
       </c>
       <c r="R33" t="n">
-        <v>6980436</v>
+        <v>6980678</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3874,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127419008</v>
+        <v>127421509</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,34 +3885,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593907</v>
+        <v>593953</v>
       </c>
       <c r="R34" t="n">
-        <v>6980678</v>
+        <v>6980432</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127421509</v>
+        <v>127419922</v>
       </c>
       <c r="B35" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593953</v>
+        <v>593925</v>
       </c>
       <c r="R35" t="n">
-        <v>6980432</v>
+        <v>6980436</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4068,32 +4068,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B36" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R36" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420200</v>
+        <v>127421293</v>
       </c>
       <c r="B38" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593873</v>
+        <v>593913</v>
       </c>
       <c r="R38" t="n">
-        <v>6980365</v>
+        <v>6980334</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419778</v>
+        <v>127421707</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,34 +4768,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593943</v>
+        <v>593964</v>
       </c>
       <c r="R43" t="n">
-        <v>6980554</v>
+        <v>6980471</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421707</v>
+        <v>127419778</v>
       </c>
       <c r="B44" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,34 +4865,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593964</v>
+        <v>593943</v>
       </c>
       <c r="R44" t="n">
-        <v>6980471</v>
+        <v>6980554</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B45" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R45" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R46" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -2700,45 +2700,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127419767</v>
+        <v>127420409</v>
       </c>
       <c r="B22" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593943</v>
+        <v>593897</v>
       </c>
       <c r="R22" t="n">
-        <v>6980554</v>
+        <v>6980226</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2797,45 +2797,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127420409</v>
+        <v>127419767</v>
       </c>
       <c r="B23" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593897</v>
+        <v>593943</v>
       </c>
       <c r="R23" t="n">
-        <v>6980226</v>
+        <v>6980554</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127420237</v>
+        <v>127420121</v>
       </c>
       <c r="B24" t="n">
-        <v>92632</v>
+        <v>56853</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2905,34 +2905,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593891</v>
+        <v>593878</v>
       </c>
       <c r="R24" t="n">
-        <v>6980346</v>
+        <v>6980391</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2965,6 +2970,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2991,10 +3001,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127421539</v>
+        <v>127420002</v>
       </c>
       <c r="B25" t="n">
-        <v>78685</v>
+        <v>78776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3002,21 +3012,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3026,10 +3036,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593955</v>
+        <v>593907</v>
       </c>
       <c r="R25" t="n">
-        <v>6980435</v>
+        <v>6980443</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3088,45 +3098,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127419220</v>
+        <v>127420237</v>
       </c>
       <c r="B26" t="n">
-        <v>78685</v>
+        <v>92632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593901</v>
+        <v>593891</v>
       </c>
       <c r="R26" t="n">
-        <v>6980651</v>
+        <v>6980346</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3185,50 +3195,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420121</v>
+        <v>127421539</v>
       </c>
       <c r="B27" t="n">
-        <v>56853</v>
+        <v>78685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593878</v>
+        <v>593955</v>
       </c>
       <c r="R27" t="n">
-        <v>6980391</v>
+        <v>6980435</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3261,11 +3266,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420002</v>
+        <v>127419220</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>78685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,34 +3303,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593907</v>
+        <v>593901</v>
       </c>
       <c r="R28" t="n">
-        <v>6980443</v>
+        <v>6980651</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R31" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B32" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R32" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420375</v>
+        <v>127420401</v>
       </c>
       <c r="B39" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593879</v>
+        <v>593888</v>
       </c>
       <c r="R39" t="n">
-        <v>6980223</v>
+        <v>6980242</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127420401</v>
+        <v>127420375</v>
       </c>
       <c r="B40" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593888</v>
+        <v>593879</v>
       </c>
       <c r="R40" t="n">
-        <v>6980242</v>
+        <v>6980223</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4553,45 +4553,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127419973</v>
+        <v>127420990</v>
       </c>
       <c r="B41" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593919</v>
+        <v>593785</v>
       </c>
       <c r="R41" t="n">
-        <v>6980452</v>
+        <v>6980249</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4624,6 +4629,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,50 +4660,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127420990</v>
+        <v>127419973</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593785</v>
+        <v>593919</v>
       </c>
       <c r="R42" t="n">
-        <v>6980249</v>
+        <v>6980452</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4726,11 +4731,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R45" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R46" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127420121</v>
+        <v>127420237</v>
       </c>
       <c r="B24" t="n">
-        <v>56853</v>
+        <v>92632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2905,39 +2905,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593878</v>
+        <v>593891</v>
       </c>
       <c r="R24" t="n">
-        <v>6980391</v>
+        <v>6980346</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2970,11 +2965,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3001,10 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420002</v>
+        <v>127421539</v>
       </c>
       <c r="B25" t="n">
-        <v>78776</v>
+        <v>78685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,21 +3002,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3036,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593907</v>
+        <v>593955</v>
       </c>
       <c r="R25" t="n">
-        <v>6980443</v>
+        <v>6980435</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3098,45 +3088,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420237</v>
+        <v>127419220</v>
       </c>
       <c r="B26" t="n">
-        <v>92632</v>
+        <v>78685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593891</v>
+        <v>593901</v>
       </c>
       <c r="R26" t="n">
-        <v>6980346</v>
+        <v>6980651</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3195,45 +3185,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127421539</v>
+        <v>127420121</v>
       </c>
       <c r="B27" t="n">
-        <v>78685</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593955</v>
+        <v>593878</v>
       </c>
       <c r="R27" t="n">
-        <v>6980435</v>
+        <v>6980391</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3266,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127419220</v>
+        <v>127420002</v>
       </c>
       <c r="B28" t="n">
-        <v>78685</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,34 +3303,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593901</v>
+        <v>593907</v>
       </c>
       <c r="R28" t="n">
-        <v>6980651</v>
+        <v>6980443</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4553,50 +4553,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127420990</v>
+        <v>127419973</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593785</v>
+        <v>593919</v>
       </c>
       <c r="R41" t="n">
-        <v>6980249</v>
+        <v>6980452</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4629,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4660,45 +4650,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419973</v>
+        <v>127420990</v>
       </c>
       <c r="B42" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593919</v>
+        <v>593785</v>
       </c>
       <c r="R42" t="n">
-        <v>6980452</v>
+        <v>6980249</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4731,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B45" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R45" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R46" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420137</v>
+        <v>127421406</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593873</v>
+        <v>593921</v>
       </c>
       <c r="R8" t="n">
-        <v>6980393</v>
+        <v>6980392</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421406</v>
+        <v>127420137</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593921</v>
+        <v>593873</v>
       </c>
       <c r="R9" t="n">
-        <v>6980392</v>
+        <v>6980393</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127419866</v>
+        <v>127419655</v>
       </c>
       <c r="B10" t="n">
         <v>92620</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593940</v>
+        <v>593933</v>
       </c>
       <c r="R10" t="n">
-        <v>6980501</v>
+        <v>6980566</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127419655</v>
+        <v>127419866</v>
       </c>
       <c r="B11" t="n">
         <v>92620</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593933</v>
+        <v>593940</v>
       </c>
       <c r="R11" t="n">
-        <v>6980566</v>
+        <v>6980501</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419287</v>
+        <v>127420036</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593904</v>
+        <v>593889</v>
       </c>
       <c r="R12" t="n">
-        <v>6980639</v>
+        <v>6980419</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420104</v>
+        <v>127419826</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593888</v>
+        <v>593938</v>
       </c>
       <c r="R13" t="n">
-        <v>6980408</v>
+        <v>6980539</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,50 +1914,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127421018</v>
+        <v>127420313</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593762</v>
+        <v>593881</v>
       </c>
       <c r="R14" t="n">
-        <v>6980239</v>
+        <v>6980236</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1990,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419978</v>
+        <v>127420104</v>
       </c>
       <c r="B15" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593931</v>
+        <v>593888</v>
       </c>
       <c r="R15" t="n">
-        <v>6980442</v>
+        <v>6980408</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,45 +2108,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420313</v>
+        <v>127419978</v>
       </c>
       <c r="B16" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593881</v>
+        <v>593931</v>
       </c>
       <c r="R16" t="n">
-        <v>6980236</v>
+        <v>6980442</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,45 +2205,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420036</v>
+        <v>127419287</v>
       </c>
       <c r="B17" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593889</v>
+        <v>593904</v>
       </c>
       <c r="R17" t="n">
-        <v>6980419</v>
+        <v>6980639</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,45 +2302,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127419826</v>
+        <v>127421018</v>
       </c>
       <c r="B18" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593938</v>
+        <v>593762</v>
       </c>
       <c r="R18" t="n">
-        <v>6980539</v>
+        <v>6980239</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2383,6 +2378,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>92624</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R20" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B21" t="n">
-        <v>92624</v>
+        <v>79636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R21" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2700,45 +2700,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127420409</v>
+        <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593897</v>
+        <v>593943</v>
       </c>
       <c r="R22" t="n">
-        <v>6980226</v>
+        <v>6980554</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2797,45 +2797,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127419767</v>
+        <v>127420409</v>
       </c>
       <c r="B23" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593943</v>
+        <v>593897</v>
       </c>
       <c r="R23" t="n">
-        <v>6980554</v>
+        <v>6980226</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3088,45 +3088,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127419220</v>
+        <v>127420121</v>
       </c>
       <c r="B26" t="n">
-        <v>78685</v>
+        <v>56853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593901</v>
+        <v>593878</v>
       </c>
       <c r="R26" t="n">
-        <v>6980651</v>
+        <v>6980391</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3159,6 +3164,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,50 +3195,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420121</v>
+        <v>127419220</v>
       </c>
       <c r="B27" t="n">
-        <v>56853</v>
+        <v>78685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593878</v>
+        <v>593901</v>
       </c>
       <c r="R27" t="n">
-        <v>6980391</v>
+        <v>6980651</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3261,11 +3266,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>92813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R29" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B30" t="n">
-        <v>92813</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R30" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R31" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B32" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R32" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3777,45 +3777,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419008</v>
+        <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593907</v>
+        <v>593925</v>
       </c>
       <c r="R33" t="n">
-        <v>6980678</v>
+        <v>6980436</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3971,45 +3971,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127419922</v>
+        <v>127419008</v>
       </c>
       <c r="B35" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593925</v>
+        <v>593907</v>
       </c>
       <c r="R35" t="n">
-        <v>6980436</v>
+        <v>6980678</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420200</v>
+        <v>127420388</v>
       </c>
       <c r="B36" t="n">
         <v>92620</v>
@@ -4099,14 +4099,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593873</v>
+        <v>593888</v>
       </c>
       <c r="R36" t="n">
-        <v>6980365</v>
+        <v>6980235</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4165,45 +4165,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420388</v>
+        <v>127421293</v>
       </c>
       <c r="B37" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593888</v>
+        <v>593913</v>
       </c>
       <c r="R37" t="n">
-        <v>6980235</v>
+        <v>6980334</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B38" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R38" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420401</v>
+        <v>127420375</v>
       </c>
       <c r="B39" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593888</v>
+        <v>593879</v>
       </c>
       <c r="R39" t="n">
-        <v>6980242</v>
+        <v>6980223</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127420375</v>
+        <v>127420401</v>
       </c>
       <c r="B40" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593879</v>
+        <v>593888</v>
       </c>
       <c r="R40" t="n">
-        <v>6980223</v>
+        <v>6980242</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R45" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R46" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421406</v>
+        <v>127420137</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593921</v>
+        <v>593873</v>
       </c>
       <c r="R8" t="n">
-        <v>6980392</v>
+        <v>6980393</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127420137</v>
+        <v>127421406</v>
       </c>
       <c r="B9" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593873</v>
+        <v>593921</v>
       </c>
       <c r="R9" t="n">
-        <v>6980393</v>
+        <v>6980392</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -3088,50 +3088,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420121</v>
+        <v>127419220</v>
       </c>
       <c r="B26" t="n">
-        <v>56853</v>
+        <v>78685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593878</v>
+        <v>593901</v>
       </c>
       <c r="R26" t="n">
-        <v>6980391</v>
+        <v>6980651</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3164,11 +3159,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3195,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127419220</v>
+        <v>127420002</v>
       </c>
       <c r="B27" t="n">
-        <v>78685</v>
+        <v>78776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,34 +3196,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593901</v>
+        <v>593907</v>
       </c>
       <c r="R27" t="n">
-        <v>6980651</v>
+        <v>6980443</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3292,45 +3282,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420002</v>
+        <v>127420121</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>56853</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593907</v>
+        <v>593878</v>
       </c>
       <c r="R28" t="n">
-        <v>6980443</v>
+        <v>6980391</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3363,6 +3358,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B29" t="n">
-        <v>92813</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R29" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>92813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R30" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420375</v>
+        <v>127420401</v>
       </c>
       <c r="B39" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593879</v>
+        <v>593888</v>
       </c>
       <c r="R39" t="n">
-        <v>6980223</v>
+        <v>6980242</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127420401</v>
+        <v>127420375</v>
       </c>
       <c r="B40" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593888</v>
+        <v>593879</v>
       </c>
       <c r="R40" t="n">
-        <v>6980242</v>
+        <v>6980223</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B45" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R45" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421181</v>
+        <v>127419423</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,34 +5059,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593779</v>
+        <v>593923</v>
       </c>
       <c r="R46" t="n">
-        <v>6980274</v>
+        <v>6980636</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5145,45 +5145,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127419423</v>
+        <v>127421244</v>
       </c>
       <c r="B47" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593923</v>
+        <v>593884</v>
       </c>
       <c r="R47" t="n">
-        <v>6980636</v>
+        <v>6980318</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>127421259</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>127420137</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>127421406</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127419655</v>
+        <v>127419866</v>
       </c>
       <c r="B10" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593933</v>
+        <v>593940</v>
       </c>
       <c r="R10" t="n">
-        <v>6980566</v>
+        <v>6980501</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127419866</v>
+        <v>127419655</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593940</v>
+        <v>593933</v>
       </c>
       <c r="R11" t="n">
-        <v>6980501</v>
+        <v>6980566</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420036</v>
+        <v>127419287</v>
       </c>
       <c r="B12" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593889</v>
+        <v>593904</v>
       </c>
       <c r="R12" t="n">
-        <v>6980419</v>
+        <v>6980639</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419826</v>
+        <v>127420104</v>
       </c>
       <c r="B13" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593938</v>
+        <v>593888</v>
       </c>
       <c r="R13" t="n">
-        <v>6980539</v>
+        <v>6980408</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,45 +1914,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420313</v>
+        <v>127421018</v>
       </c>
       <c r="B14" t="n">
-        <v>92620</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593881</v>
+        <v>593762</v>
       </c>
       <c r="R14" t="n">
-        <v>6980236</v>
+        <v>6980239</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1985,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,45 +2021,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420104</v>
+        <v>127420313</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593888</v>
+        <v>593881</v>
       </c>
       <c r="R15" t="n">
-        <v>6980408</v>
+        <v>6980236</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,32 +2118,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127419978</v>
+        <v>127420036</v>
       </c>
       <c r="B16" t="n">
-        <v>78777</v>
+        <v>92622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593931</v>
+        <v>593889</v>
       </c>
       <c r="R16" t="n">
-        <v>6980442</v>
+        <v>6980419</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,45 +2215,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127419287</v>
+        <v>127419826</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593904</v>
+        <v>593938</v>
       </c>
       <c r="R17" t="n">
-        <v>6980639</v>
+        <v>6980539</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2302,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127421018</v>
+        <v>127419978</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>78779</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,39 +2323,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593762</v>
+        <v>593931</v>
       </c>
       <c r="R18" t="n">
-        <v>6980239</v>
+        <v>6980442</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2378,11 +2383,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,7 +2412,7 @@
         <v>127419756</v>
       </c>
       <c r="B19" t="n">
-        <v>91591</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127421852</v>
       </c>
       <c r="B20" t="n">
-        <v>92624</v>
+        <v>92626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>127421272</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>127420409</v>
       </c>
       <c r="B23" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2894,45 +2894,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127420237</v>
+        <v>127419220</v>
       </c>
       <c r="B24" t="n">
-        <v>92632</v>
+        <v>78687</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593891</v>
+        <v>593901</v>
       </c>
       <c r="R24" t="n">
-        <v>6980346</v>
+        <v>6980651</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2991,32 +2991,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127421539</v>
+        <v>127420237</v>
       </c>
       <c r="B25" t="n">
-        <v>78685</v>
+        <v>92634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593955</v>
+        <v>593891</v>
       </c>
       <c r="R25" t="n">
-        <v>6980435</v>
+        <v>6980346</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3088,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127419220</v>
+        <v>127420002</v>
       </c>
       <c r="B26" t="n">
-        <v>78685</v>
+        <v>78778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,34 +3099,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593901</v>
+        <v>593907</v>
       </c>
       <c r="R26" t="n">
-        <v>6980651</v>
+        <v>6980443</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420002</v>
+        <v>127421539</v>
       </c>
       <c r="B27" t="n">
-        <v>78776</v>
+        <v>78687</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593907</v>
+        <v>593955</v>
       </c>
       <c r="R27" t="n">
-        <v>6980443</v>
+        <v>6980435</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3285,7 +3285,7 @@
         <v>127420121</v>
       </c>
       <c r="B28" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>127420170</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127419859</v>
       </c>
       <c r="B30" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127419760</v>
       </c>
       <c r="B32" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>127421509</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>127419008</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420388</v>
+        <v>127420200</v>
       </c>
       <c r="B36" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4099,14 +4099,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593888</v>
+        <v>593873</v>
       </c>
       <c r="R36" t="n">
-        <v>6980235</v>
+        <v>6980365</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4165,45 +4165,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127421293</v>
+        <v>127420388</v>
       </c>
       <c r="B37" t="n">
-        <v>78685</v>
+        <v>92622</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593913</v>
+        <v>593888</v>
       </c>
       <c r="R37" t="n">
-        <v>6980334</v>
+        <v>6980235</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420200</v>
+        <v>127421293</v>
       </c>
       <c r="B38" t="n">
-        <v>92620</v>
+        <v>78687</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593873</v>
+        <v>593913</v>
       </c>
       <c r="R38" t="n">
-        <v>6980365</v>
+        <v>6980334</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420401</v>
+        <v>127420375</v>
       </c>
       <c r="B39" t="n">
-        <v>78777</v>
+        <v>78687</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593888</v>
+        <v>593879</v>
       </c>
       <c r="R39" t="n">
-        <v>6980242</v>
+        <v>6980223</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127420375</v>
+        <v>127420401</v>
       </c>
       <c r="B40" t="n">
-        <v>78685</v>
+        <v>78779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593879</v>
+        <v>593888</v>
       </c>
       <c r="R40" t="n">
-        <v>6980223</v>
+        <v>6980242</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4556,7 +4556,7 @@
         <v>127419973</v>
       </c>
       <c r="B41" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>127420990</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421707</v>
+        <v>127419778</v>
       </c>
       <c r="B43" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,34 +4768,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593964</v>
+        <v>593943</v>
       </c>
       <c r="R43" t="n">
-        <v>6980471</v>
+        <v>6980554</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127419778</v>
+        <v>127421707</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,34 +4865,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593943</v>
+        <v>593964</v>
       </c>
       <c r="R44" t="n">
-        <v>6980554</v>
+        <v>6980471</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4954,7 +4954,7 @@
         <v>127421181</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127419423</v>
+        <v>127421244</v>
       </c>
       <c r="B46" t="n">
-        <v>78777</v>
+        <v>92622</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593923</v>
+        <v>593884</v>
       </c>
       <c r="R46" t="n">
-        <v>6980636</v>
+        <v>6980318</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5145,45 +5145,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421244</v>
+        <v>127419423</v>
       </c>
       <c r="B47" t="n">
-        <v>92620</v>
+        <v>78779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593884</v>
+        <v>593923</v>
       </c>
       <c r="R47" t="n">
-        <v>6980318</v>
+        <v>6980636</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5245,7 +5245,7 @@
         <v>127421618</v>
       </c>
       <c r="B48" t="n">
-        <v>91621</v>
+        <v>91623</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127421800</v>
       </c>
       <c r="B49" t="n">
-        <v>91615</v>
+        <v>91617</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419287</v>
+        <v>127420104</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,34 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593904</v>
+        <v>593888</v>
       </c>
       <c r="R12" t="n">
-        <v>6980639</v>
+        <v>6980408</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420104</v>
+        <v>127420036</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593888</v>
+        <v>593889</v>
       </c>
       <c r="R13" t="n">
-        <v>6980408</v>
+        <v>6980419</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,50 +1914,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127421018</v>
+        <v>127419826</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593762</v>
+        <v>593938</v>
       </c>
       <c r="R14" t="n">
-        <v>6980239</v>
+        <v>6980539</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1990,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,45 +2108,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420036</v>
+        <v>127419287</v>
       </c>
       <c r="B16" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593889</v>
+        <v>593904</v>
       </c>
       <c r="R16" t="n">
-        <v>6980419</v>
+        <v>6980639</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,45 +2205,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127419826</v>
+        <v>127421018</v>
       </c>
       <c r="B17" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593938</v>
+        <v>593762</v>
       </c>
       <c r="R17" t="n">
-        <v>6980539</v>
+        <v>6980239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2286,6 +2281,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2894,7 +2894,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127419220</v>
+        <v>127421539</v>
       </c>
       <c r="B24" t="n">
         <v>78687</v>
@@ -2925,14 +2925,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593901</v>
+        <v>593955</v>
       </c>
       <c r="R24" t="n">
-        <v>6980651</v>
+        <v>6980435</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2991,45 +2991,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420237</v>
+        <v>127419220</v>
       </c>
       <c r="B25" t="n">
-        <v>92634</v>
+        <v>78687</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593891</v>
+        <v>593901</v>
       </c>
       <c r="R25" t="n">
-        <v>6980346</v>
+        <v>6980651</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3185,45 +3185,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127421539</v>
+        <v>127420121</v>
       </c>
       <c r="B27" t="n">
-        <v>78687</v>
+        <v>56855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593955</v>
+        <v>593878</v>
       </c>
       <c r="R27" t="n">
-        <v>6980435</v>
+        <v>6980391</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3256,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420121</v>
+        <v>127420237</v>
       </c>
       <c r="B28" t="n">
-        <v>56855</v>
+        <v>92634</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,39 +3303,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593878</v>
+        <v>593891</v>
       </c>
       <c r="R28" t="n">
-        <v>6980391</v>
+        <v>6980346</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3358,11 +3363,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B31" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R31" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B32" t="n">
-        <v>78687</v>
+        <v>92622</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R32" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4068,32 +4068,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420200</v>
+        <v>127421293</v>
       </c>
       <c r="B36" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593873</v>
+        <v>593913</v>
       </c>
       <c r="R36" t="n">
-        <v>6980365</v>
+        <v>6980334</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B38" t="n">
-        <v>78687</v>
+        <v>92622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R38" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419778</v>
+        <v>127421707</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,34 +4768,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593943</v>
+        <v>593964</v>
       </c>
       <c r="R43" t="n">
-        <v>6980554</v>
+        <v>6980471</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421707</v>
+        <v>127419778</v>
       </c>
       <c r="B44" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,34 +4865,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593964</v>
+        <v>593943</v>
       </c>
       <c r="R44" t="n">
-        <v>6980471</v>
+        <v>6980554</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R45" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R46" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1817,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420036</v>
+        <v>127419978</v>
       </c>
       <c r="B13" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593889</v>
+        <v>593931</v>
       </c>
       <c r="R13" t="n">
-        <v>6980419</v>
+        <v>6980442</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419826</v>
+        <v>127420036</v>
       </c>
       <c r="B14" t="n">
         <v>92622</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593938</v>
+        <v>593889</v>
       </c>
       <c r="R14" t="n">
-        <v>6980539</v>
+        <v>6980419</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420313</v>
+        <v>127419826</v>
       </c>
       <c r="B15" t="n">
         <v>92622</v>
@@ -2042,14 +2042,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593881</v>
+        <v>593938</v>
       </c>
       <c r="R15" t="n">
-        <v>6980236</v>
+        <v>6980539</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,45 +2108,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127419287</v>
+        <v>127420313</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593904</v>
+        <v>593881</v>
       </c>
       <c r="R16" t="n">
-        <v>6980639</v>
+        <v>6980236</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127421018</v>
+        <v>127419287</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,39 +2216,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593762</v>
+        <v>593904</v>
       </c>
       <c r="R17" t="n">
-        <v>6980239</v>
+        <v>6980639</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2281,11 +2276,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127419978</v>
+        <v>127421018</v>
       </c>
       <c r="B18" t="n">
-        <v>78779</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,34 +2313,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593931</v>
+        <v>593762</v>
       </c>
       <c r="R18" t="n">
-        <v>6980442</v>
+        <v>6980239</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2383,6 +2378,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B20" t="n">
-        <v>92626</v>
+        <v>79638</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R20" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B21" t="n">
-        <v>79638</v>
+        <v>92626</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B29" t="n">
-        <v>92622</v>
+        <v>92815</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R29" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B30" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R30" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1720,32 +1720,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420104</v>
+        <v>127419826</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593888</v>
+        <v>593938</v>
       </c>
       <c r="R12" t="n">
-        <v>6980408</v>
+        <v>6980539</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419978</v>
+        <v>127419287</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,34 +1828,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593931</v>
+        <v>593904</v>
       </c>
       <c r="R13" t="n">
-        <v>6980442</v>
+        <v>6980639</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419826</v>
+        <v>127420313</v>
       </c>
       <c r="B15" t="n">
         <v>92622</v>
@@ -2042,14 +2042,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593938</v>
+        <v>593881</v>
       </c>
       <c r="R15" t="n">
-        <v>6980539</v>
+        <v>6980236</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,45 +2108,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420313</v>
+        <v>127420104</v>
       </c>
       <c r="B16" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593881</v>
+        <v>593888</v>
       </c>
       <c r="R16" t="n">
-        <v>6980236</v>
+        <v>6980408</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127419287</v>
+        <v>127421018</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,34 +2216,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593904</v>
+        <v>593762</v>
       </c>
       <c r="R17" t="n">
-        <v>6980639</v>
+        <v>6980239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2276,6 +2281,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2302,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127421018</v>
+        <v>127419978</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>78779</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,39 +2323,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593762</v>
+        <v>593931</v>
       </c>
       <c r="R18" t="n">
-        <v>6980239</v>
+        <v>6980442</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2378,11 +2383,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B20" t="n">
-        <v>79638</v>
+        <v>92626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R20" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B21" t="n">
-        <v>92626</v>
+        <v>79638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R21" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420121</v>
+        <v>127420237</v>
       </c>
       <c r="B27" t="n">
-        <v>56855</v>
+        <v>92634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3196,39 +3196,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593878</v>
+        <v>593891</v>
       </c>
       <c r="R27" t="n">
-        <v>6980391</v>
+        <v>6980346</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3261,11 +3256,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420237</v>
+        <v>127420121</v>
       </c>
       <c r="B28" t="n">
-        <v>92634</v>
+        <v>56855</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,34 +3293,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593891</v>
+        <v>593878</v>
       </c>
       <c r="R28" t="n">
-        <v>6980346</v>
+        <v>6980391</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3363,6 +3358,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B29" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R29" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>92815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R30" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3874,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127421509</v>
+        <v>127419008</v>
       </c>
       <c r="B34" t="n">
-        <v>78778</v>
+        <v>79638</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,34 +3885,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593953</v>
+        <v>593907</v>
       </c>
       <c r="R34" t="n">
-        <v>6980432</v>
+        <v>6980678</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3971,10 +3971,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127419008</v>
+        <v>127421509</v>
       </c>
       <c r="B35" t="n">
-        <v>79638</v>
+        <v>78778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593907</v>
+        <v>593953</v>
       </c>
       <c r="R35" t="n">
-        <v>6980678</v>
+        <v>6980432</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4553,45 +4553,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127419973</v>
+        <v>127420990</v>
       </c>
       <c r="B41" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593919</v>
+        <v>593785</v>
       </c>
       <c r="R41" t="n">
-        <v>6980452</v>
+        <v>6980249</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4624,6 +4629,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,50 +4660,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127420990</v>
+        <v>127419973</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593785</v>
+        <v>593919</v>
       </c>
       <c r="R42" t="n">
-        <v>6980249</v>
+        <v>6980452</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4726,11 +4731,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421707</v>
+        <v>127419778</v>
       </c>
       <c r="B43" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,34 +4768,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593964</v>
+        <v>593943</v>
       </c>
       <c r="R43" t="n">
-        <v>6980471</v>
+        <v>6980554</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127419778</v>
+        <v>127421707</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,34 +4865,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593943</v>
+        <v>593964</v>
       </c>
       <c r="R44" t="n">
-        <v>6980554</v>
+        <v>6980471</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B45" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R45" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421181</v>
+        <v>127419423</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,34 +5059,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593779</v>
+        <v>593923</v>
       </c>
       <c r="R46" t="n">
-        <v>6980274</v>
+        <v>6980636</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5145,45 +5145,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127419423</v>
+        <v>127421244</v>
       </c>
       <c r="B47" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593923</v>
+        <v>593884</v>
       </c>
       <c r="R47" t="n">
-        <v>6980636</v>
+        <v>6980318</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1335,7 +1335,7 @@
         <v>127420137</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>127419866</v>
       </c>
       <c r="B10" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>127419655</v>
       </c>
       <c r="B11" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419826</v>
+        <v>127420036</v>
       </c>
       <c r="B12" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593938</v>
+        <v>593889</v>
       </c>
       <c r="R12" t="n">
-        <v>6980539</v>
+        <v>6980419</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420036</v>
+        <v>127419826</v>
       </c>
       <c r="B14" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593889</v>
+        <v>593938</v>
       </c>
       <c r="R14" t="n">
-        <v>6980419</v>
+        <v>6980539</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2014,7 +2014,7 @@
         <v>127420313</v>
       </c>
       <c r="B15" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420104</v>
+        <v>127421018</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,34 +2119,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593888</v>
+        <v>593762</v>
       </c>
       <c r="R16" t="n">
-        <v>6980408</v>
+        <v>6980239</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2179,6 +2184,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127421018</v>
+        <v>127420104</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,39 +2226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593762</v>
+        <v>593888</v>
       </c>
       <c r="R17" t="n">
-        <v>6980239</v>
+        <v>6980408</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2281,11 +2286,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,7 +2412,7 @@
         <v>127419756</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127421852</v>
       </c>
       <c r="B20" t="n">
-        <v>92626</v>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127421539</v>
+        <v>127420002</v>
       </c>
       <c r="B24" t="n">
-        <v>78687</v>
+        <v>78778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2905,21 +2905,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593955</v>
+        <v>593907</v>
       </c>
       <c r="R24" t="n">
-        <v>6980435</v>
+        <v>6980443</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2991,45 +2991,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127419220</v>
+        <v>127420121</v>
       </c>
       <c r="B25" t="n">
-        <v>78687</v>
+        <v>56855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593901</v>
+        <v>593878</v>
       </c>
       <c r="R25" t="n">
-        <v>6980651</v>
+        <v>6980391</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3062,6 +3067,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3088,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420002</v>
+        <v>127421539</v>
       </c>
       <c r="B26" t="n">
-        <v>78778</v>
+        <v>78687</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593907</v>
+        <v>593955</v>
       </c>
       <c r="R26" t="n">
-        <v>6980443</v>
+        <v>6980435</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3185,45 +3195,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420237</v>
+        <v>127419220</v>
       </c>
       <c r="B27" t="n">
-        <v>92634</v>
+        <v>78687</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593891</v>
+        <v>593901</v>
       </c>
       <c r="R27" t="n">
-        <v>6980346</v>
+        <v>6980651</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3282,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420121</v>
+        <v>127420237</v>
       </c>
       <c r="B28" t="n">
-        <v>56855</v>
+        <v>92640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,39 +3303,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593878</v>
+        <v>593891</v>
       </c>
       <c r="R28" t="n">
-        <v>6980391</v>
+        <v>6980346</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3358,11 +3363,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3392,7 +3392,7 @@
         <v>127420170</v>
       </c>
       <c r="B29" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127419859</v>
       </c>
       <c r="B30" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>78687</v>
+        <v>92628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R31" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B32" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R32" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3780,7 +3780,7 @@
         <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,45 +4068,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127421293</v>
+        <v>127420388</v>
       </c>
       <c r="B36" t="n">
-        <v>78687</v>
+        <v>92628</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593913</v>
+        <v>593888</v>
       </c>
       <c r="R36" t="n">
-        <v>6980334</v>
+        <v>6980235</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4165,10 +4165,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420388</v>
+        <v>127420200</v>
       </c>
       <c r="B37" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593888</v>
+        <v>593873</v>
       </c>
       <c r="R37" t="n">
-        <v>6980235</v>
+        <v>6980365</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420200</v>
+        <v>127421293</v>
       </c>
       <c r="B38" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593873</v>
+        <v>593913</v>
       </c>
       <c r="R38" t="n">
-        <v>6980365</v>
+        <v>6980334</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4553,50 +4553,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127420990</v>
+        <v>127419973</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>92628</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593785</v>
+        <v>593919</v>
       </c>
       <c r="R41" t="n">
-        <v>6980249</v>
+        <v>6980452</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4629,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4660,45 +4650,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419973</v>
+        <v>127420990</v>
       </c>
       <c r="B42" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593919</v>
+        <v>593785</v>
       </c>
       <c r="R42" t="n">
-        <v>6980452</v>
+        <v>6980249</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4731,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R45" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127419423</v>
+        <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,34 +5059,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593923</v>
+        <v>593779</v>
       </c>
       <c r="R46" t="n">
-        <v>6980636</v>
+        <v>6980274</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5145,45 +5145,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127421244</v>
+        <v>127419423</v>
       </c>
       <c r="B47" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593884</v>
+        <v>593923</v>
       </c>
       <c r="R47" t="n">
-        <v>6980318</v>
+        <v>6980636</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5245,7 +5245,7 @@
         <v>127421618</v>
       </c>
       <c r="B48" t="n">
-        <v>91623</v>
+        <v>91629</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127421800</v>
       </c>
       <c r="B49" t="n">
-        <v>91617</v>
+        <v>91623</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>127421259</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420137</v>
+        <v>127421406</v>
       </c>
       <c r="B8" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593873</v>
+        <v>593921</v>
       </c>
       <c r="R8" t="n">
-        <v>6980393</v>
+        <v>6980392</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421406</v>
+        <v>127420137</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593921</v>
+        <v>593873</v>
       </c>
       <c r="R9" t="n">
-        <v>6980392</v>
+        <v>6980393</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1529,7 +1529,7 @@
         <v>127419866</v>
       </c>
       <c r="B10" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>127419655</v>
       </c>
       <c r="B11" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,32 +1720,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420036</v>
+        <v>127420104</v>
       </c>
       <c r="B12" t="n">
-        <v>92628</v>
+        <v>79641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593889</v>
+        <v>593888</v>
       </c>
       <c r="R12" t="n">
-        <v>6980419</v>
+        <v>6980408</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,45 +1817,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419287</v>
+        <v>127420036</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593904</v>
+        <v>593889</v>
       </c>
       <c r="R13" t="n">
-        <v>6980639</v>
+        <v>6980419</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,45 +1914,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419826</v>
+        <v>127419287</v>
       </c>
       <c r="B14" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593938</v>
+        <v>593904</v>
       </c>
       <c r="R14" t="n">
-        <v>6980539</v>
+        <v>6980639</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420313</v>
+        <v>127419826</v>
       </c>
       <c r="B15" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,14 +2042,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593881</v>
+        <v>593938</v>
       </c>
       <c r="R15" t="n">
-        <v>6980236</v>
+        <v>6980539</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,50 +2108,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127421018</v>
+        <v>127420313</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593762</v>
+        <v>593881</v>
       </c>
       <c r="R16" t="n">
-        <v>6980239</v>
+        <v>6980236</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2184,11 +2179,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420104</v>
+        <v>127421018</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,34 +2216,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593888</v>
+        <v>593762</v>
       </c>
       <c r="R17" t="n">
-        <v>6980408</v>
+        <v>6980239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2286,6 +2281,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,7 +2315,7 @@
         <v>127419978</v>
       </c>
       <c r="B18" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>127419756</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B20" t="n">
-        <v>92632</v>
+        <v>79641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R20" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B21" t="n">
-        <v>79638</v>
+        <v>92635</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2703,7 +2703,7 @@
         <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>127420409</v>
       </c>
       <c r="B23" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127420002</v>
+        <v>127421539</v>
       </c>
       <c r="B24" t="n">
-        <v>78778</v>
+        <v>78690</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2905,21 +2905,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593907</v>
+        <v>593955</v>
       </c>
       <c r="R24" t="n">
-        <v>6980443</v>
+        <v>6980435</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2991,50 +2991,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127420121</v>
+        <v>127419220</v>
       </c>
       <c r="B25" t="n">
-        <v>56855</v>
+        <v>78690</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593878</v>
+        <v>593901</v>
       </c>
       <c r="R25" t="n">
-        <v>6980391</v>
+        <v>6980651</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3067,11 +3062,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3098,32 +3088,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127421539</v>
+        <v>127420237</v>
       </c>
       <c r="B26" t="n">
-        <v>78687</v>
+        <v>92643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593955</v>
+        <v>593891</v>
       </c>
       <c r="R26" t="n">
-        <v>6980435</v>
+        <v>6980346</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3195,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127419220</v>
+        <v>127420002</v>
       </c>
       <c r="B27" t="n">
-        <v>78687</v>
+        <v>78781</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,34 +3196,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593901</v>
+        <v>593907</v>
       </c>
       <c r="R27" t="n">
-        <v>6980651</v>
+        <v>6980443</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3292,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420237</v>
+        <v>127420121</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>56858</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,34 +3293,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593891</v>
+        <v>593878</v>
       </c>
       <c r="R28" t="n">
-        <v>6980346</v>
+        <v>6980391</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3363,6 +3358,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3392,7 +3392,7 @@
         <v>127420170</v>
       </c>
       <c r="B29" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127419859</v>
       </c>
       <c r="B30" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B31" t="n">
-        <v>92628</v>
+        <v>78690</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R31" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B32" t="n">
-        <v>78687</v>
+        <v>92631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R32" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3780,7 +3780,7 @@
         <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>127419008</v>
       </c>
       <c r="B34" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>127421509</v>
       </c>
       <c r="B35" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4068,45 +4068,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420388</v>
+        <v>127421293</v>
       </c>
       <c r="B36" t="n">
-        <v>92628</v>
+        <v>78690</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593888</v>
+        <v>593913</v>
       </c>
       <c r="R36" t="n">
-        <v>6980235</v>
+        <v>6980334</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4165,10 +4165,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420200</v>
+        <v>127420388</v>
       </c>
       <c r="B37" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593873</v>
+        <v>593888</v>
       </c>
       <c r="R37" t="n">
-        <v>6980365</v>
+        <v>6980235</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B38" t="n">
-        <v>78687</v>
+        <v>92631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R38" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4362,7 +4362,7 @@
         <v>127420375</v>
       </c>
       <c r="B39" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>127420401</v>
       </c>
       <c r="B40" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,45 +4553,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127419973</v>
+        <v>127420990</v>
       </c>
       <c r="B41" t="n">
-        <v>92628</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593919</v>
+        <v>593785</v>
       </c>
       <c r="R41" t="n">
-        <v>6980452</v>
+        <v>6980249</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4624,6 +4629,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,50 +4660,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127420990</v>
+        <v>127419973</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593785</v>
+        <v>593919</v>
       </c>
       <c r="R42" t="n">
-        <v>6980249</v>
+        <v>6980452</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4726,11 +4731,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419778</v>
+        <v>127421707</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>78781</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,34 +4768,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593943</v>
+        <v>593964</v>
       </c>
       <c r="R43" t="n">
-        <v>6980554</v>
+        <v>6980471</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421707</v>
+        <v>127419778</v>
       </c>
       <c r="B44" t="n">
-        <v>78778</v>
+        <v>79023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,34 +4865,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593964</v>
+        <v>593943</v>
       </c>
       <c r="R44" t="n">
-        <v>6980471</v>
+        <v>6980554</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4954,7 +4954,7 @@
         <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>127419423</v>
       </c>
       <c r="B47" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>127421618</v>
       </c>
       <c r="B48" t="n">
-        <v>91629</v>
+        <v>91632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127421800</v>
       </c>
       <c r="B49" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>127421259</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421406</v>
+        <v>127420137</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593921</v>
+        <v>593873</v>
       </c>
       <c r="R8" t="n">
-        <v>6980392</v>
+        <v>6980393</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127420137</v>
+        <v>127421406</v>
       </c>
       <c r="B9" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593873</v>
+        <v>593921</v>
       </c>
       <c r="R9" t="n">
-        <v>6980393</v>
+        <v>6980392</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1529,7 +1529,7 @@
         <v>127419866</v>
       </c>
       <c r="B10" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>127419655</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,32 +1720,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420104</v>
+        <v>127420036</v>
       </c>
       <c r="B12" t="n">
-        <v>79641</v>
+        <v>92639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593888</v>
+        <v>593889</v>
       </c>
       <c r="R12" t="n">
-        <v>6980408</v>
+        <v>6980419</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420036</v>
+        <v>127419826</v>
       </c>
       <c r="B13" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593889</v>
+        <v>593938</v>
       </c>
       <c r="R13" t="n">
-        <v>6980419</v>
+        <v>6980539</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,45 +1914,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419287</v>
+        <v>127420313</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593904</v>
+        <v>593881</v>
       </c>
       <c r="R14" t="n">
-        <v>6980639</v>
+        <v>6980236</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,32 +2011,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419826</v>
+        <v>127420104</v>
       </c>
       <c r="B15" t="n">
-        <v>92631</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593938</v>
+        <v>593888</v>
       </c>
       <c r="R15" t="n">
-        <v>6980539</v>
+        <v>6980408</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,45 +2108,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420313</v>
+        <v>127419287</v>
       </c>
       <c r="B16" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593881</v>
+        <v>593904</v>
       </c>
       <c r="R16" t="n">
-        <v>6980236</v>
+        <v>6980639</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2208,7 +2208,7 @@
         <v>127421018</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>127419978</v>
       </c>
       <c r="B18" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>127419756</v>
       </c>
       <c r="B19" t="n">
-        <v>91602</v>
+        <v>91610</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127421272</v>
       </c>
       <c r="B20" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>127421852</v>
       </c>
       <c r="B21" t="n">
-        <v>92635</v>
+        <v>92643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>127420409</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>127421539</v>
       </c>
       <c r="B24" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>127419220</v>
       </c>
       <c r="B25" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3088,32 +3088,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420237</v>
+        <v>127420002</v>
       </c>
       <c r="B26" t="n">
-        <v>92643</v>
+        <v>78787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593891</v>
+        <v>593907</v>
       </c>
       <c r="R26" t="n">
-        <v>6980346</v>
+        <v>6980443</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3185,32 +3185,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420002</v>
+        <v>127420237</v>
       </c>
       <c r="B27" t="n">
-        <v>78781</v>
+        <v>92651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593907</v>
+        <v>593891</v>
       </c>
       <c r="R27" t="n">
-        <v>6980443</v>
+        <v>6980346</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3285,7 +3285,7 @@
         <v>127420121</v>
       </c>
       <c r="B28" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B29" t="n">
-        <v>92631</v>
+        <v>92832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R29" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B30" t="n">
-        <v>92824</v>
+        <v>92639</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R30" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>78690</v>
+        <v>92639</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R31" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B32" t="n">
-        <v>92631</v>
+        <v>78696</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R32" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3780,7 +3780,7 @@
         <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>127419008</v>
       </c>
       <c r="B34" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>127421509</v>
       </c>
       <c r="B35" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>127421293</v>
       </c>
       <c r="B36" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>127420388</v>
       </c>
       <c r="B37" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>127420200</v>
       </c>
       <c r="B38" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>127420375</v>
       </c>
       <c r="B39" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>127420401</v>
       </c>
       <c r="B40" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,50 +4553,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127420990</v>
+        <v>127419973</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593785</v>
+        <v>593919</v>
       </c>
       <c r="R41" t="n">
-        <v>6980249</v>
+        <v>6980452</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4629,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4660,45 +4650,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419973</v>
+        <v>127420990</v>
       </c>
       <c r="B42" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593919</v>
+        <v>593785</v>
       </c>
       <c r="R42" t="n">
-        <v>6980452</v>
+        <v>6980249</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4731,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4760,7 +4760,7 @@
         <v>127421707</v>
       </c>
       <c r="B43" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>127419778</v>
       </c>
       <c r="B44" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>127419423</v>
       </c>
       <c r="B47" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>127421618</v>
       </c>
       <c r="B48" t="n">
-        <v>91632</v>
+        <v>91640</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127421800</v>
       </c>
       <c r="B49" t="n">
-        <v>91626</v>
+        <v>91634</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1335,7 +1335,7 @@
         <v>127420137</v>
       </c>
       <c r="B8" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>127419866</v>
       </c>
       <c r="B10" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>127419655</v>
       </c>
       <c r="B11" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420036</v>
+        <v>127419826</v>
       </c>
       <c r="B12" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593889</v>
+        <v>593938</v>
       </c>
       <c r="R12" t="n">
-        <v>6980419</v>
+        <v>6980539</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,45 +1817,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419826</v>
+        <v>127419287</v>
       </c>
       <c r="B13" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593938</v>
+        <v>593904</v>
       </c>
       <c r="R13" t="n">
-        <v>6980539</v>
+        <v>6980639</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,45 +1914,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420313</v>
+        <v>127420104</v>
       </c>
       <c r="B14" t="n">
-        <v>92639</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593881</v>
+        <v>593888</v>
       </c>
       <c r="R14" t="n">
-        <v>6980236</v>
+        <v>6980408</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420104</v>
+        <v>127421018</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,34 +2022,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593888</v>
+        <v>593762</v>
       </c>
       <c r="R15" t="n">
-        <v>6980408</v>
+        <v>6980239</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2082,6 +2087,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,45 +2118,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127419287</v>
+        <v>127420036</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593904</v>
+        <v>593889</v>
       </c>
       <c r="R16" t="n">
-        <v>6980639</v>
+        <v>6980419</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,50 +2215,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127421018</v>
+        <v>127420313</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593762</v>
+        <v>593881</v>
       </c>
       <c r="R17" t="n">
-        <v>6980239</v>
+        <v>6980236</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2281,11 +2286,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,7 +2412,7 @@
         <v>127419756</v>
       </c>
       <c r="B19" t="n">
-        <v>91610</v>
+        <v>91611</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>92644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R20" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B21" t="n">
-        <v>92643</v>
+        <v>79647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R21" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2703,7 +2703,7 @@
         <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,32 +3088,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420002</v>
+        <v>127420237</v>
       </c>
       <c r="B26" t="n">
-        <v>78787</v>
+        <v>92652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593907</v>
+        <v>593891</v>
       </c>
       <c r="R26" t="n">
-        <v>6980443</v>
+        <v>6980346</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420237</v>
+        <v>127420121</v>
       </c>
       <c r="B27" t="n">
-        <v>92651</v>
+        <v>56864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3196,34 +3196,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593891</v>
+        <v>593878</v>
       </c>
       <c r="R27" t="n">
-        <v>6980346</v>
+        <v>6980391</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3256,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,50 +3292,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420121</v>
+        <v>127420002</v>
       </c>
       <c r="B28" t="n">
-        <v>56864</v>
+        <v>78787</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593878</v>
+        <v>593907</v>
       </c>
       <c r="R28" t="n">
-        <v>6980391</v>
+        <v>6980443</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3358,11 +3363,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3392,7 +3392,7 @@
         <v>127419859</v>
       </c>
       <c r="B29" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127420170</v>
       </c>
       <c r="B30" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>127420388</v>
       </c>
       <c r="B37" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>127420200</v>
       </c>
       <c r="B38" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4553,45 +4553,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127419973</v>
+        <v>127420990</v>
       </c>
       <c r="B41" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593919</v>
+        <v>593785</v>
       </c>
       <c r="R41" t="n">
-        <v>6980452</v>
+        <v>6980249</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4624,6 +4629,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,50 +4660,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127420990</v>
+        <v>127419973</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593785</v>
+        <v>593919</v>
       </c>
       <c r="R42" t="n">
-        <v>6980249</v>
+        <v>6980452</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4726,11 +4731,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4954,7 +4954,7 @@
         <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>127421618</v>
       </c>
       <c r="B48" t="n">
-        <v>91640</v>
+        <v>91641</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127421800</v>
       </c>
       <c r="B49" t="n">
-        <v>91634</v>
+        <v>91635</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1720,45 +1720,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419826</v>
+        <v>127421018</v>
       </c>
       <c r="B12" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593938</v>
+        <v>593762</v>
       </c>
       <c r="R12" t="n">
-        <v>6980539</v>
+        <v>6980239</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1791,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,45 +1827,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127419287</v>
+        <v>127420036</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593904</v>
+        <v>593889</v>
       </c>
       <c r="R13" t="n">
-        <v>6980639</v>
+        <v>6980419</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,32 +1924,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420104</v>
+        <v>127419826</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>92640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593888</v>
+        <v>593938</v>
       </c>
       <c r="R14" t="n">
-        <v>6980408</v>
+        <v>6980539</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,50 +2021,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127421018</v>
+        <v>127420313</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593762</v>
+        <v>593881</v>
       </c>
       <c r="R15" t="n">
-        <v>6980239</v>
+        <v>6980236</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2087,11 +2092,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,45 +2118,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420036</v>
+        <v>127419287</v>
       </c>
       <c r="B16" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593889</v>
+        <v>593904</v>
       </c>
       <c r="R16" t="n">
-        <v>6980419</v>
+        <v>6980639</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,45 +2215,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420313</v>
+        <v>127420104</v>
       </c>
       <c r="B17" t="n">
-        <v>92640</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593881</v>
+        <v>593888</v>
       </c>
       <c r="R17" t="n">
-        <v>6980236</v>
+        <v>6980408</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -3185,50 +3185,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420121</v>
+        <v>127420002</v>
       </c>
       <c r="B27" t="n">
-        <v>56864</v>
+        <v>78787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593878</v>
+        <v>593907</v>
       </c>
       <c r="R27" t="n">
-        <v>6980391</v>
+        <v>6980443</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3261,11 +3256,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,45 +3282,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420002</v>
+        <v>127420121</v>
       </c>
       <c r="B28" t="n">
-        <v>78787</v>
+        <v>56864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593907</v>
+        <v>593878</v>
       </c>
       <c r="R28" t="n">
-        <v>6980443</v>
+        <v>6980391</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3363,6 +3358,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B29" t="n">
-        <v>92833</v>
+        <v>92640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R29" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>92833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R30" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3777,32 +3777,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127419922</v>
+        <v>127421509</v>
       </c>
       <c r="B33" t="n">
-        <v>92640</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593925</v>
+        <v>593953</v>
       </c>
       <c r="R33" t="n">
-        <v>6980436</v>
+        <v>6980432</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127421509</v>
+        <v>127419922</v>
       </c>
       <c r="B35" t="n">
-        <v>78787</v>
+        <v>92640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593953</v>
+        <v>593925</v>
       </c>
       <c r="R35" t="n">
-        <v>6980432</v>
+        <v>6980436</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4068,45 +4068,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127421293</v>
+        <v>127420388</v>
       </c>
       <c r="B36" t="n">
-        <v>78696</v>
+        <v>92640</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593913</v>
+        <v>593888</v>
       </c>
       <c r="R36" t="n">
-        <v>6980334</v>
+        <v>6980235</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420388</v>
+        <v>127420200</v>
       </c>
       <c r="B37" t="n">
         <v>92640</v>
@@ -4196,14 +4196,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593888</v>
+        <v>593873</v>
       </c>
       <c r="R37" t="n">
-        <v>6980235</v>
+        <v>6980365</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420200</v>
+        <v>127421293</v>
       </c>
       <c r="B38" t="n">
-        <v>92640</v>
+        <v>78696</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593873</v>
+        <v>593913</v>
       </c>
       <c r="R38" t="n">
-        <v>6980365</v>
+        <v>6980334</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420375</v>
+        <v>127420401</v>
       </c>
       <c r="B39" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593879</v>
+        <v>593888</v>
       </c>
       <c r="R39" t="n">
-        <v>6980223</v>
+        <v>6980242</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127420401</v>
+        <v>127420375</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>78696</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593888</v>
+        <v>593879</v>
       </c>
       <c r="R40" t="n">
-        <v>6980242</v>
+        <v>6980223</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4553,50 +4553,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127420990</v>
+        <v>127419973</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593785</v>
+        <v>593919</v>
       </c>
       <c r="R41" t="n">
-        <v>6980249</v>
+        <v>6980452</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4629,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4660,45 +4650,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127419973</v>
+        <v>127420990</v>
       </c>
       <c r="B42" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593919</v>
+        <v>593785</v>
       </c>
       <c r="R42" t="n">
-        <v>6980452</v>
+        <v>6980249</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4731,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B45" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R45" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R46" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1335,7 +1335,7 @@
         <v>127420137</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>127419866</v>
       </c>
       <c r="B10" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>127419655</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127421018</v>
+        <v>127419287</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593762</v>
+        <v>593904</v>
       </c>
       <c r="R12" t="n">
-        <v>6980239</v>
+        <v>6980639</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1796,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420036</v>
+        <v>127420104</v>
       </c>
       <c r="B13" t="n">
-        <v>92640</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593889</v>
+        <v>593888</v>
       </c>
       <c r="R13" t="n">
-        <v>6980419</v>
+        <v>6980408</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1924,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127419826</v>
+        <v>127420036</v>
       </c>
       <c r="B14" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593938</v>
+        <v>593889</v>
       </c>
       <c r="R14" t="n">
-        <v>6980539</v>
+        <v>6980419</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127420313</v>
+        <v>127419826</v>
       </c>
       <c r="B15" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,14 +2042,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593881</v>
+        <v>593938</v>
       </c>
       <c r="R15" t="n">
-        <v>6980236</v>
+        <v>6980539</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,45 +2108,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127419287</v>
+        <v>127420313</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593904</v>
+        <v>593881</v>
       </c>
       <c r="R16" t="n">
-        <v>6980639</v>
+        <v>6980236</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127420104</v>
+        <v>127421018</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,34 +2216,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593888</v>
+        <v>593762</v>
       </c>
       <c r="R17" t="n">
-        <v>6980408</v>
+        <v>6980239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2286,6 +2281,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,7 +2412,7 @@
         <v>127419756</v>
       </c>
       <c r="B19" t="n">
-        <v>91611</v>
+        <v>91612</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B20" t="n">
-        <v>92644</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R20" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B21" t="n">
-        <v>79647</v>
+        <v>92645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2703,7 +2703,7 @@
         <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,32 +3088,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420237</v>
+        <v>127420002</v>
       </c>
       <c r="B26" t="n">
-        <v>92652</v>
+        <v>78787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593891</v>
+        <v>593907</v>
       </c>
       <c r="R26" t="n">
-        <v>6980346</v>
+        <v>6980443</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3185,45 +3185,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420002</v>
+        <v>127420121</v>
       </c>
       <c r="B27" t="n">
-        <v>78787</v>
+        <v>56864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593907</v>
+        <v>593878</v>
       </c>
       <c r="R27" t="n">
-        <v>6980443</v>
+        <v>6980391</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3256,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420121</v>
+        <v>127420237</v>
       </c>
       <c r="B28" t="n">
-        <v>56864</v>
+        <v>92653</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,39 +3303,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593878</v>
+        <v>593891</v>
       </c>
       <c r="R28" t="n">
-        <v>6980391</v>
+        <v>6980346</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3358,11 +3363,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B29" t="n">
-        <v>92640</v>
+        <v>92834</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R29" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B30" t="n">
-        <v>92833</v>
+        <v>92641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R30" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3586,7 +3586,7 @@
         <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,32 +3777,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127421509</v>
+        <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>78787</v>
+        <v>92641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593953</v>
+        <v>593925</v>
       </c>
       <c r="R33" t="n">
-        <v>6980432</v>
+        <v>6980436</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127419922</v>
+        <v>127421509</v>
       </c>
       <c r="B35" t="n">
-        <v>92640</v>
+        <v>78787</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593925</v>
+        <v>593953</v>
       </c>
       <c r="R35" t="n">
-        <v>6980436</v>
+        <v>6980432</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4068,45 +4068,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420388</v>
+        <v>127421293</v>
       </c>
       <c r="B36" t="n">
-        <v>92640</v>
+        <v>78696</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593888</v>
+        <v>593913</v>
       </c>
       <c r="R36" t="n">
-        <v>6980235</v>
+        <v>6980334</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4165,10 +4165,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127420200</v>
+        <v>127420388</v>
       </c>
       <c r="B37" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593873</v>
+        <v>593888</v>
       </c>
       <c r="R37" t="n">
-        <v>6980365</v>
+        <v>6980235</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B38" t="n">
-        <v>78696</v>
+        <v>92641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R38" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127420401</v>
+        <v>127420375</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>78696</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593888</v>
+        <v>593879</v>
       </c>
       <c r="R39" t="n">
-        <v>6980242</v>
+        <v>6980223</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127420375</v>
+        <v>127420401</v>
       </c>
       <c r="B40" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593879</v>
+        <v>593888</v>
       </c>
       <c r="R40" t="n">
-        <v>6980223</v>
+        <v>6980242</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4556,7 +4556,7 @@
         <v>127419973</v>
       </c>
       <c r="B41" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>127421244</v>
       </c>
       <c r="B46" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>127421618</v>
       </c>
       <c r="B48" t="n">
-        <v>91641</v>
+        <v>91642</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127421800</v>
       </c>
       <c r="B49" t="n">
-        <v>91635</v>
+        <v>91636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127420137</v>
+        <v>127421406</v>
       </c>
       <c r="B8" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593873</v>
+        <v>593921</v>
       </c>
       <c r="R8" t="n">
-        <v>6980393</v>
+        <v>6980392</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127421406</v>
+        <v>127420137</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593921</v>
+        <v>593873</v>
       </c>
       <c r="R9" t="n">
-        <v>6980392</v>
+        <v>6980393</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1529,7 +1529,7 @@
         <v>127419866</v>
       </c>
       <c r="B10" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>127419655</v>
       </c>
       <c r="B11" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127419287</v>
+        <v>127420313</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593904</v>
+        <v>593881</v>
       </c>
       <c r="R12" t="n">
-        <v>6980639</v>
+        <v>6980236</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127420104</v>
+        <v>127420036</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593888</v>
+        <v>593889</v>
       </c>
       <c r="R13" t="n">
-        <v>6980408</v>
+        <v>6980419</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127420036</v>
+        <v>127419826</v>
       </c>
       <c r="B14" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593889</v>
+        <v>593938</v>
       </c>
       <c r="R14" t="n">
-        <v>6980419</v>
+        <v>6980539</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,45 +2011,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419826</v>
+        <v>127419287</v>
       </c>
       <c r="B15" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593938</v>
+        <v>593904</v>
       </c>
       <c r="R15" t="n">
-        <v>6980539</v>
+        <v>6980639</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,45 +2108,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420313</v>
+        <v>127420104</v>
       </c>
       <c r="B16" t="n">
-        <v>92641</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593881</v>
+        <v>593888</v>
       </c>
       <c r="R16" t="n">
-        <v>6980236</v>
+        <v>6980408</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2412,7 +2412,7 @@
         <v>127419756</v>
       </c>
       <c r="B19" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>92646</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R20" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B21" t="n">
-        <v>92645</v>
+        <v>79647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R21" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2703,7 +2703,7 @@
         <v>127419767</v>
       </c>
       <c r="B22" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,32 +3088,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127420002</v>
+        <v>127420237</v>
       </c>
       <c r="B26" t="n">
-        <v>78787</v>
+        <v>92654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593907</v>
+        <v>593891</v>
       </c>
       <c r="R26" t="n">
-        <v>6980443</v>
+        <v>6980346</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3292,32 +3292,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420237</v>
+        <v>127420002</v>
       </c>
       <c r="B28" t="n">
-        <v>92653</v>
+        <v>78787</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593891</v>
+        <v>593907</v>
       </c>
       <c r="R28" t="n">
-        <v>6980346</v>
+        <v>6980443</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B29" t="n">
-        <v>92834</v>
+        <v>92642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R29" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B30" t="n">
-        <v>92641</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R30" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3586,7 +3586,7 @@
         <v>127421307</v>
       </c>
       <c r="B31" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127419922</v>
       </c>
       <c r="B33" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3874,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127419008</v>
+        <v>127421509</v>
       </c>
       <c r="B34" t="n">
-        <v>79647</v>
+        <v>78787</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,34 +3885,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593907</v>
+        <v>593953</v>
       </c>
       <c r="R34" t="n">
-        <v>6980678</v>
+        <v>6980432</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3971,10 +3971,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127421509</v>
+        <v>127419008</v>
       </c>
       <c r="B35" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593953</v>
+        <v>593907</v>
       </c>
       <c r="R35" t="n">
-        <v>6980432</v>
+        <v>6980678</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4068,32 +4068,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B36" t="n">
-        <v>78696</v>
+        <v>92642</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R36" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4168,7 +4168,7 @@
         <v>127420388</v>
       </c>
       <c r="B37" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127420200</v>
+        <v>127421293</v>
       </c>
       <c r="B38" t="n">
-        <v>92641</v>
+        <v>78696</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593873</v>
+        <v>593913</v>
       </c>
       <c r="R38" t="n">
-        <v>6980365</v>
+        <v>6980334</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4556,7 +4556,7 @@
         <v>127419973</v>
       </c>
       <c r="B41" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127421707</v>
+        <v>127419778</v>
       </c>
       <c r="B43" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,34 +4768,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593964</v>
+        <v>593943</v>
       </c>
       <c r="R43" t="n">
-        <v>6980471</v>
+        <v>6980554</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127419778</v>
+        <v>127421707</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,34 +4865,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593943</v>
+        <v>593964</v>
       </c>
       <c r="R44" t="n">
-        <v>6980554</v>
+        <v>6980471</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R45" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B46" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R46" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5245,7 +5245,7 @@
         <v>127421618</v>
       </c>
       <c r="B48" t="n">
-        <v>91642</v>
+        <v>91643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>127421800</v>
       </c>
       <c r="B49" t="n">
-        <v>91636</v>
+        <v>91637</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127420313</v>
+        <v>127419978</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartviken, Svartviken, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593881</v>
+        <v>593931</v>
       </c>
       <c r="R12" t="n">
-        <v>6980236</v>
+        <v>6980442</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2011,45 +2011,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127419287</v>
+        <v>127420313</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartviken, Svartviken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593904</v>
+        <v>593881</v>
       </c>
       <c r="R15" t="n">
-        <v>6980639</v>
+        <v>6980236</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127420104</v>
+        <v>127419287</v>
       </c>
       <c r="B16" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,34 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593888</v>
+        <v>593904</v>
       </c>
       <c r="R16" t="n">
-        <v>6980408</v>
+        <v>6980639</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127421018</v>
+        <v>127420104</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,39 +2216,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593762</v>
+        <v>593888</v>
       </c>
       <c r="R17" t="n">
-        <v>6980239</v>
+        <v>6980408</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2281,11 +2276,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127419978</v>
+        <v>127421018</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,34 +2313,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593931</v>
+        <v>593762</v>
       </c>
       <c r="R18" t="n">
-        <v>6980442</v>
+        <v>6980239</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2383,6 +2378,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,45 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127421852</v>
+        <v>127421272</v>
       </c>
       <c r="B20" t="n">
-        <v>92646</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593957</v>
+        <v>593916</v>
       </c>
       <c r="R20" t="n">
-        <v>6980531</v>
+        <v>6980341</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,45 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127421272</v>
+        <v>127421852</v>
       </c>
       <c r="B21" t="n">
-        <v>79647</v>
+        <v>92646</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593916</v>
+        <v>593957</v>
       </c>
       <c r="R21" t="n">
-        <v>6980341</v>
+        <v>6980531</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3185,50 +3185,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127420121</v>
+        <v>127420002</v>
       </c>
       <c r="B27" t="n">
-        <v>56864</v>
+        <v>78787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593878</v>
+        <v>593907</v>
       </c>
       <c r="R27" t="n">
-        <v>6980391</v>
+        <v>6980443</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3261,11 +3256,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,45 +3282,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127420002</v>
+        <v>127420121</v>
       </c>
       <c r="B28" t="n">
-        <v>78787</v>
+        <v>56864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593907</v>
+        <v>593878</v>
       </c>
       <c r="R28" t="n">
-        <v>6980443</v>
+        <v>6980391</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3363,6 +3358,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3389,32 +3389,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127420170</v>
+        <v>127419859</v>
       </c>
       <c r="B29" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593884</v>
+        <v>593940</v>
       </c>
       <c r="R29" t="n">
-        <v>6980384</v>
+        <v>6980502</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127419859</v>
+        <v>127420170</v>
       </c>
       <c r="B30" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593940</v>
+        <v>593884</v>
       </c>
       <c r="R30" t="n">
-        <v>6980502</v>
+        <v>6980384</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3583,45 +3583,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127421307</v>
+        <v>127419760</v>
       </c>
       <c r="B31" t="n">
-        <v>92642</v>
+        <v>78696</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593909</v>
+        <v>593943</v>
       </c>
       <c r="R31" t="n">
-        <v>6980352</v>
+        <v>6980554</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3680,45 +3680,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127419760</v>
+        <v>127421307</v>
       </c>
       <c r="B32" t="n">
-        <v>78696</v>
+        <v>92642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593943</v>
+        <v>593909</v>
       </c>
       <c r="R32" t="n">
-        <v>6980554</v>
+        <v>6980352</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3874,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127421509</v>
+        <v>127419008</v>
       </c>
       <c r="B34" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,34 +3885,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593953</v>
+        <v>593907</v>
       </c>
       <c r="R34" t="n">
-        <v>6980432</v>
+        <v>6980678</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3971,10 +3971,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127419008</v>
+        <v>127421509</v>
       </c>
       <c r="B35" t="n">
-        <v>79647</v>
+        <v>78787</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vittertjärnen, Vittertjärnen, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593907</v>
+        <v>593953</v>
       </c>
       <c r="R35" t="n">
-        <v>6980678</v>
+        <v>6980432</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4068,32 +4068,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127420200</v>
+        <v>127421293</v>
       </c>
       <c r="B36" t="n">
-        <v>92642</v>
+        <v>78696</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593873</v>
+        <v>593913</v>
       </c>
       <c r="R36" t="n">
-        <v>6980365</v>
+        <v>6980334</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127421293</v>
+        <v>127420200</v>
       </c>
       <c r="B38" t="n">
-        <v>78696</v>
+        <v>92642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593913</v>
+        <v>593873</v>
       </c>
       <c r="R38" t="n">
-        <v>6980334</v>
+        <v>6980365</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127419778</v>
+        <v>127421707</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,34 +4768,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593943</v>
+        <v>593964</v>
       </c>
       <c r="R43" t="n">
-        <v>6980554</v>
+        <v>6980471</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127421707</v>
+        <v>127419778</v>
       </c>
       <c r="B44" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,34 +4865,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593964</v>
+        <v>593943</v>
       </c>
       <c r="R44" t="n">
-        <v>6980471</v>
+        <v>6980554</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4951,45 +4951,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421244</v>
+        <v>127421181</v>
       </c>
       <c r="B45" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593884</v>
+        <v>593779</v>
       </c>
       <c r="R45" t="n">
-        <v>6980318</v>
+        <v>6980274</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5048,45 +5048,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127421181</v>
+        <v>127421244</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Svartvikmyran, Svartvikmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593779</v>
+        <v>593884</v>
       </c>
       <c r="R46" t="n">
-        <v>6980274</v>
+        <v>6980318</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 45687-2024 artfynd.xlsx
+++ b/artfynd/A 45687-2024 artfynd.xlsx
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127421406</v>
+        <v>127420137</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593921</v>
+        <v>593873</v>
       </c>
       <c r="R8" t="n">
-        <v>6980392</v>
+        <v>6980393</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127420137</v>
+        <v>127421406</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593873</v>
+        <v>593921</v>
       </c>
       <c r="R9" t="n">
-        <v>6980393</v>
+        <v>6980392</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127421181</v>
+        <v>127419423</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,34 +4962,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
+          <t>Sundet, Sundet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593779</v>
+        <v>593923</v>
       </c>
       <c r="R45" t="n">
-        <v>6980274</v>
+        <v>6980636</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5145,10 +5145,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127419423</v>
+        <v>127421181</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,34 +5156,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundet, Sundet, Jmt</t>
+          <t>Lill-Gussjön, Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593923</v>
+        <v>593779</v>
       </c>
       <c r="R47" t="n">
-        <v>6980636</v>
+        <v>6980274</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
